--- a/data/trans_dic/P79$alquiler_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79$alquiler_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,46</t>
+          <t>0,33; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,04</t>
+          <t>0,69; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,47</t>
+          <t>0,66; 1,7</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,75</t>
+          <t>0,74; 2,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,69</t>
+          <t>1,51; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,14</t>
+          <t>1,3; 2,63</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,76</t>
+          <t>0,75; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,64</t>
+          <t>0,81; 3,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,52</t>
+          <t>1,01; 2,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,95</t>
+          <t>2,44; 5,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,27</t>
+          <t>2,4; 4,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,6</t>
+          <t>2,75; 4,5</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,95</t>
+          <t>1,41; 2,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,49</t>
+          <t>1,88; 2,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,78; 2,54</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>14915</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1289; 9043</t>
+          <t>2195; 11162</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3994; 14391</t>
+          <t>4930; 16055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6546; 19406</t>
+          <t>9125; 23510</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>38202</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3879; 20467</t>
+          <t>7524; 26058</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12336; 34026</t>
+          <t>15546; 37551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18201; 44770</t>
+          <t>26684; 53948</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>25151</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5191; 18684</t>
+          <t>5740; 19693</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2633; 32932</t>
+          <t>6314; 28842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10426; 39820</t>
+          <t>15574; 39515</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>71284</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14367; 35459</t>
+          <t>23452; 49068</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20730; 42205</t>
+          <t>25859; 50990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39703; 67954</t>
+          <t>55998; 91816</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34323; 65621</t>
+          <t>48295; 85539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48871; 87640</t>
+          <t>67680; 105514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90124; 146012</t>
+          <t>125300; 178156</t>
         </is>
       </c>
     </row>
